--- a/02_加值成品/生物/生物2-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物2-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物2-2 植物的營養：光合作用　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國一(七年級) 生物2-2 植物的營養：光合作用　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>植物自製養分的作用是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>氧氣</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>葉綠素</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>葉綠體</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>光合作用</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>製養分</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>光合作用在哪個胞器進行？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>光合作用</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>氧氣</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>葉綠體</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>二氧化碳與水</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>綠色</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>光合作用需要的原料？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>化學能</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>二氧化碳與水</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>促進光合</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>呼吸作用</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>原料</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>光合作用釋出什麼氣體？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>變黃(黃化)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>葉綠體</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>氧氣</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>葡萄糖</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>放氧</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>光合作用製造的養分是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>葡萄糖</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>化學能</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>葉綠體</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>氣孔</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>醣類</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>調節氣體進出的構造是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>葡萄糖</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>葉綠素</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>氣孔</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>水分</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>孔</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>植物在生態系中是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>光合作用</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>呼吸作用</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>生產者</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>葉綠體</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>自製</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>光合作用把光能轉為？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>化學能</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>葉綠體</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>二氧化碳與水</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>氧氣</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>轉換</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>光合作用需要哪種光？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>光合製養放氧、呼吸耗養耗氧,互補</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>陽光(可見光)</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>行光合放氧吸碳調節氣候</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>生產者自製養分供應能量與氧</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>光</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>葉的綠色來自哪種色素？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>氣孔</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>葡萄糖</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>光合作用</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>葉綠素</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>色素</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物2-2 植物的營養：光合作用　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國一(七年級) 生物2-2 植物的營養：光合作用　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>影響光合作用的因素？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>葉肉細胞(含葉綠體)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>葡萄糖</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>光合旺盛淨釋氧</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>光CO₂溫度</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>三者</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>氣孔多分布在葉的？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>光合作用</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>變黃(黃化)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>氧氣</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>背面</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>葉背</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>蒸散作用散失的是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>促進光合</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>氣孔</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>水分</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>葡萄糖</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>植物晚上進行什麼作用？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>葡萄糖</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>氧氣</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>二氧化碳與水</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>呼吸作用</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>獲能</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>光合作用吸收哪種氣體？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>光合作用</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>二氧化碳與水</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>水分</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>二氧化碳</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>吸收</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>溫室補充CO₂為了？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>光合作用</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>水分</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>促進光合</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>增產</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>植物有光合也有呼吸嗎？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>二氧化碳與水</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>有</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>光合作用</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>變黃(黃化)</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>兩者</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>光越強光合作用一般？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>生產者自製養分供應能量與氧</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>偏離適溫酵素受影響光合下降</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>越快(有限度)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>陽光(可見光)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>光線</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>光合作用主要在葉的哪種細胞進行？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>光合製養放氧、呼吸耗養耗氧,互補</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>越快(有限度)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>陽光(可見光)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>葉肉細胞(含葉綠體)</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>部位</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>植物長期缺光葉子可能？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>光合作用</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>二氧化碳與水</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>生產者</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>變黃(黃化)</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>缺葉綠素</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國一(七年級) 生物2-2 植物的營養：光合作用　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國一(七年級) 生物2-2 植物的營養：光合作用　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>寫出光合作用的反應物與產物？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>光合作用釋出氧</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>越快(有限度)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>CO₂與水→葡萄糖與氧(光能葉綠體)</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>光合製養放氧、呼吸耗養耗氧,互補</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>反應</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>比較光合作用與呼吸作用的關係？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>葉肉細胞(含葉綠體)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>行光合放氧吸碳調節氣候</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>光合製養放氧、呼吸耗養耗氧,互補</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>CO₂與水→葡萄糖與氧(光能葉綠體)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>關係</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>氣孔如何兼顧氣體交換與水分散失？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>葉肉細胞(含葉綠體)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>強光較快至飽和</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>開啟利氣體進出但也蒸散失水需調節</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>CO₂與水→葡萄糖與氧(光能葉綠體)</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>平衡</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>為何說植物是生態系基礎？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>光合製養放氧、呼吸耗養耗氧,互補</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>陽光(可見光)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>生產者自製養分供應能量與氧</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>光合減少養分不足生長受阻</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>基礎</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>光照不足對植物生長影響？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>越快(有限度)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>光合減少養分不足生長受阻</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>行光合放氧吸碳調節氣候</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>偏離適溫酵素受影響光合下降</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>光線</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>植物白天氣體交換淨結果？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>CO₂與水→葡萄糖與氧(光能葉綠體)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>光合製養放氧、呼吸耗養耗氧,互補</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>偏離適溫酵素受影響光合下降</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>光合旺盛淨釋氧</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>淨值</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>溫度過高過低對光合影響？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>越快(有限度)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>偏離適溫酵素受影響光合下降</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>光合作用釋出氧</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>CO₂與水→葡萄糖與氧(光能葉綠體)</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>溫度</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>森林對大氣的貢獻？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>行光合放氧吸碳調節氣候</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>越快(有限度)</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>光合旺盛淨釋氧</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>陽光(可見光)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>貢獻</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何水生植物白天在水中冒氣泡？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>行光合放氧吸碳調節氣候</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>光合作用釋出氧</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>光合旺盛淨釋氧</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>CO₂與水→葡萄糖與氧(光能葉綠體)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>放氧</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>比較植物在強光與弱光下光合速率？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>偏離適溫酵素受影響光合下降</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>光合作用釋出氧</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>光合製養放氧、呼吸耗養耗氧,互補</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>強光較快至飽和</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>光強</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/生物/生物2-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物2-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>製養分</t>
+          <t>自製養分：植物能利用光能，把簡單的原料轉變成養分，這個過程叫光合作用</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>綠色</t>
+          <t>在葉綠體：光合作用是在含有葉綠素的葉綠體中進行，能吸收光能</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>原料</t>
+          <t>所需原料：光合作用需要利用二氧化碳和水這兩種原料，加上光能來製造養分</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>放氧</t>
+          <t>釋出氧氣：光合作用進行時會把水分解，並把多餘的氧氣釋放到空氣中</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>醣類</t>
+          <t>製造葡萄糖：光合作用最後會製造出葡萄糖，這是植物主要儲存能量的養分</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>孔</t>
+          <t>調節氣體：葉片上的氣孔能開閉，用來控制二氧化碳、氧氣與水氣的進出</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>自製</t>
+          <t>生態系生產者：植物能自己製造養分，供應其他生物所需能量，所以是生產者</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>轉換</t>
+          <t>能量轉換：光合作用能把光的能量轉變成儲存在葡萄糖裡的化學能</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>光</t>
+          <t>光：植物行光合作用需要吸收陽光中的可見光作為能量來源，把光能轉換成化學能</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>色素</t>
+          <t>色素：葉綠體中含有葉綠素，能吸收光能進行光合作用，也使葉子呈現綠色</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>三者</t>
+          <t>三大因素：光線強弱、二氧化碳濃度和溫度，都會影響光合作用進行的速率</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>葉背</t>
+          <t>多在葉背：為了減少水分散失，大多數植物的氣孔集中分布在葉片背面</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>水</t>
+          <t>散失水分：植物體內的水分會經由氣孔蒸發到空氣中，這叫做蒸散作用</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>獲能</t>
+          <t>進行呼吸：沒有陽光時植物無法行光合作用，但仍會持續進行呼吸作用獲取能量</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>吸收</t>
+          <t>吸收二氧化碳：光合作用需要吸收空氣中的二氧化碳當作製造養分的原料</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>增產</t>
+          <t>促進光合：溫室內提高二氧化碳濃度，可以讓植物光合作用進行得更快，增加產量</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>兩者</t>
+          <t>兩者並存：植物白天有光時同時進行光合作用和呼吸作用，兩種作用都在運作</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>光線</t>
+          <t>光線影響：光線越強光合作用速率通常越快，但強到一定程度後就不再增加</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>部位</t>
+          <t>部位：葉肉細胞內含有大量葉綠體，是進行光合作用最主要的場所</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>缺葉綠素</t>
+          <t>缺葉綠素：植物長期缺乏光照，無法正常製造葉綠素，葉子會因此變黃，這種現象稱為黃化</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>反應</t>
+          <t>完整反應：光合作用在葉綠體中利用光能，把二氧化碳和水轉變成葡萄糖和氧氣</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>關係</t>
+          <t>互補關係：光合作用製造養分並釋放氧氣，呼吸作用則消耗養分和氧氣，兩者互補</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>權衡調節：氣孔打開方便氣體進出，但也會讓水分散失，植物需適時調節開合</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>基礎</t>
+          <t>生態基礎：植物身為生產者，自己製造養分並供應能量與氧氣給其他生物使用</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>光線</t>
+          <t>生長受阻：光線不足會使光合作用減弱，植物製造的養分變少，生長因而受到阻礙</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>淨值</t>
+          <t>淨釋放氧氣：白天光合作用比呼吸作用旺盛，整體來看植物淨釋放出氧氣</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>溫度</t>
+          <t>溫度影響：溫度太高或太低都會讓體內酵素作用不良，使光合作用速率下降</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>貢獻</t>
+          <t>調節氣候：森林大量進行光合作用，釋放氧氣並吸收二氧化碳，有助調節氣候</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>放氧</t>
+          <t>放氧：水生植物白天行光合作用會產生氧氣，多餘的氧氣以氣泡的形式從葉片排出，在水中可以看到一顆顆小氣泡</t>
         </is>
       </c>
     </row>
@@ -1870,37 +1870,37 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>比較植物在強光與弱光下光合速率？</t>
+          <t>比較植物在強光與弱光下的光合速率？</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>偏離適溫酵素受影響光合下降</t>
+          <t>強光較快至飽和</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>光合作用釋出氧</t>
+          <t>陽光(可見光)</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>光合製養放氧、呼吸耗養耗氧,互補</t>
+          <t>葉肉細胞(含葉綠體)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>強光較快至飽和</t>
+          <t>CO₂與水→葡萄糖與氧(光能葉綠體)</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>光強</t>
+          <t>光強：光線越強，光合作用的速率通常越快，但當光線強度達到一定程度後，速率會趨於穩定不再增加，稱為光飽和</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/生物/生物2-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/生物/生物2-2_三種難度測驗卷.xlsx
@@ -643,7 +643,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>化學能</t>
+          <t>背面</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -653,12 +653,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>葡萄糖</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>促進光合</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>呼吸作用</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1039,17 +1039,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>葉肉細胞(含葉綠體)</t>
+          <t>強光較快至飽和</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>葡萄糖</t>
+          <t>變黃(黃化)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>光合旺盛淨釋氧</t>
+          <t>越快(有限度)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>光合作用</t>
+          <t>生產者</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>二氧化碳與水</t>
+          <t>呼吸作用</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>水分</t>
+          <t>有</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
